--- a/exports/HDFCBANK_full_report.xlsx
+++ b/exports/HDFCBANK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>4.06</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>764.5</v>
+        <v>747.6</v>
       </c>
       <c r="I2" t="n">
         <v>752.3164187000001</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.33</v>
+        <v>-3.51</v>
       </c>
       <c r="L2" t="n">
         <v>3.98</v>
       </c>
       <c r="M2" t="n">
-        <v>0.89</v>
+        <v>1.24</v>
       </c>
       <c r="N2" t="n">
-        <v>1.75</v>
+        <v>2.9</v>
       </c>
       <c r="O2" t="n">
         <v>0.53</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>5.24</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44594.38541666666</v>
+        <v>44594.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>765.4</v>
+        <v>767.5</v>
       </c>
       <c r="I3" t="n">
         <v>766.1660340449421</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.38</v>
+        <v>-2.66</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="M3" t="n">
         <v>1.6</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>5.4</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44599.55208333334</v>
+        <v>44600.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>735.5</v>
+        <v>725.1</v>
       </c>
       <c r="I4" t="n">
         <v>727.2457848907511</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.17</v>
+        <v>-5.52</v>
       </c>
       <c r="L4" t="n">
-        <v>4.89</v>
+        <v>5.89</v>
       </c>
       <c r="M4" t="n">
         <v>0.6</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>6.03</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44601.55208333334</v>
+        <v>44602.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>749.2</v>
+        <v>766.6</v>
       </c>
       <c r="I5" t="n">
         <v>766.2825358336869</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.32</v>
+        <v>-5.72</v>
       </c>
       <c r="L5" t="n">
-        <v>3.41</v>
+        <v>5.89</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>6.05</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44616.38541666666</v>
+        <v>44616.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>729</v>
+        <v>705.1</v>
       </c>
       <c r="I6" t="n">
         <v>727.5979623870571</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.9</v>
+        <v>-8.02</v>
       </c>
       <c r="L6" t="n">
-        <v>5.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M6" t="n">
         <v>3.33</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>7.42</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>685.5</v>
+        <v>701.3</v>
       </c>
       <c r="I7" t="n">
         <v>698.903514808982</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>2.78</v>
+        <v>0.54</v>
       </c>
       <c r="L7" t="n">
         <v>3.93</v>
       </c>
       <c r="M7" t="n">
-        <v>2.11</v>
+        <v>4.08</v>
       </c>
       <c r="N7" t="n">
         <v>3.28</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.96</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44658.38541666666</v>
+        <v>44658.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>764.6</v>
+        <v>760.5</v>
       </c>
       <c r="I8" t="n">
         <v>763.4172310595937</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>9.029999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="L8" t="n">
         <v>2.12</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.1</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44706.55208333334</v>
+        <v>44707.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>663.4</v>
+        <v>680.3</v>
       </c>
       <c r="I9" t="n">
         <v>674.8720767376301</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>48</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K9" t="n">
-        <v>12.77</v>
+        <v>10.55</v>
       </c>
       <c r="L9" t="n">
         <v>0.66</v>
@@ -954,7 +1061,7 @@
         <v>1.45</v>
       </c>
       <c r="N9" t="n">
-        <v>2.56</v>
+        <v>3.23</v>
       </c>
       <c r="O9" t="n">
         <v>-1.91</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.29</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44722.38541666666</v>
+        <v>44722.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>675.5</v>
+        <v>674.4</v>
       </c>
       <c r="I10" t="n">
         <v>675.4762437964046</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.71</v>
+        <v>-0.87</v>
       </c>
       <c r="L10" t="n">
         <v>1.51</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>3.74</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44732.55208333334</v>
+        <v>44733.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>661</v>
+        <v>676.6</v>
       </c>
       <c r="I11" t="n">
         <v>667.6517312592578</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>1.99</v>
+        <v>-0.33</v>
       </c>
       <c r="L11" t="n">
         <v>0.36</v>
       </c>
       <c r="M11" t="n">
-        <v>0.62</v>
+        <v>1.12</v>
       </c>
       <c r="N11" t="n">
         <v>1.94</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.47</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44755.38541666666</v>
+        <v>44755.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>681.7</v>
+        <v>679.6</v>
       </c>
       <c r="I12" t="n">
         <v>680.157715614288</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>0.75</v>
+        <v>0.44</v>
       </c>
       <c r="L12" t="n">
         <v>2.57</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>3.52</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44764.38541666666</v>
+        <v>44764.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>693.4</v>
+        <v>697.2</v>
       </c>
       <c r="I13" t="n">
         <v>695.4823463988357</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.03</v>
+        <v>-2.59</v>
       </c>
       <c r="L13" t="n">
-        <v>2.24</v>
+        <v>2.78</v>
       </c>
       <c r="M13" t="n">
         <v>0.88</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>3.37</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44795.55208333334</v>
+        <v>44796.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>734.4</v>
+        <v>729.6</v>
       </c>
       <c r="I14" t="n">
         <v>733.495892451703</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>31</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>5.34</v>
+        <v>4.65</v>
       </c>
       <c r="L14" t="n">
         <v>0.8</v>
       </c>
       <c r="M14" t="n">
-        <v>0.52</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
         <v>1.58</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>3.58</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44806.55208333334</v>
+        <v>44809.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="I15" t="n">
         <v>745.9207110597349</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.56</v>
+        <v>-2.25</v>
       </c>
       <c r="L15" t="n">
-        <v>2.12</v>
+        <v>2.52</v>
       </c>
       <c r="M15" t="n">
         <v>0.62</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>3.66</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44826.55208333334</v>
+        <v>44827.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>743.1</v>
+        <v>721.7</v>
       </c>
       <c r="I16" t="n">
         <v>740.7551548437008</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.39</v>
+        <v>-3.26</v>
       </c>
       <c r="L16" t="n">
-        <v>1.39</v>
+        <v>3.49</v>
       </c>
       <c r="M16" t="n">
         <v>1.32</v>
       </c>
       <c r="N16" t="n">
-        <v>2.06</v>
+        <v>2.62</v>
       </c>
       <c r="O16" t="n">
         <v>0.8100000000000001</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>5.3</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44837.55208333334</v>
+        <v>44838.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>705.5</v>
+        <v>725.6</v>
       </c>
       <c r="I17" t="n">
         <v>721.0929357810295</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K17" t="n">
-        <v>2.24</v>
+        <v>-0.54</v>
       </c>
       <c r="L17" t="n">
         <v>2.19</v>
       </c>
       <c r="M17" t="n">
-        <v>0.68</v>
+        <v>1.32</v>
       </c>
       <c r="N17" t="n">
-        <v>2.94</v>
+        <v>3.22</v>
       </c>
       <c r="O17" t="n">
         <v>-2.62</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.58</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>812.5</v>
+        <v>810</v>
       </c>
       <c r="I18" t="n">
         <v>811.3555162654244</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>78</v>
+        <v>78.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>11.98</v>
+        <v>11.63</v>
       </c>
       <c r="L18" t="n">
         <v>4.63</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>2.88</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44943.55208333334</v>
+        <v>44944.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>804</v>
+        <v>817.8</v>
       </c>
       <c r="I19" t="n">
         <v>812.2796744113763</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>0.74</v>
+        <v>-0.96</v>
       </c>
       <c r="L19" t="n">
         <v>1.58</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>4.79</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>825.4</v>
+        <v>808.1</v>
       </c>
       <c r="I20" t="n">
         <v>819.47012545579</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>9</v>
       </c>
       <c r="K20" t="n">
-        <v>0.93</v>
+        <v>-1.19</v>
       </c>
       <c r="L20" t="n">
-        <v>1.91</v>
+        <v>2.78</v>
       </c>
       <c r="M20" t="n">
-        <v>0.19</v>
+        <v>1.14</v>
       </c>
       <c r="N20" t="n">
         <v>2.49</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>4.3</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44993.55208333334</v>
+        <v>44994.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>815</v>
+        <v>818.5</v>
       </c>
       <c r="I21" t="n">
         <v>817.3766689903747</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.85</v>
+        <v>-1.29</v>
       </c>
       <c r="L21" t="n">
         <v>4.07</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>3.05</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44995.55208333334</v>
+        <v>44998.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>794.5</v>
+        <v>787.8</v>
       </c>
       <c r="I22" t="n">
         <v>793.5502239145776</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.93</v>
+        <v>-3.75</v>
       </c>
       <c r="L22" t="n">
-        <v>3.18</v>
+        <v>3.85</v>
       </c>
       <c r="M22" t="n">
         <v>1.2</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>4.44</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45016.38541666666</v>
+        <v>45016.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>800.7</v>
+        <v>804.6</v>
       </c>
       <c r="I23" t="n">
         <v>803.1872269443048</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.64</v>
+        <v>-2.13</v>
       </c>
       <c r="L23" t="n">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="M23" t="n">
         <v>0.64</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>3.58</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45050.55208333334</v>
+        <v>45051.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>864.1</v>
+        <v>819.2</v>
       </c>
       <c r="I24" t="n">
         <v>836.4704415165212</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K24" t="n">
-        <v>7.39</v>
+        <v>1.81</v>
       </c>
       <c r="L24" t="n">
         <v>0.6</v>
       </c>
       <c r="M24" t="n">
-        <v>0.34</v>
+        <v>5.16</v>
       </c>
       <c r="N24" t="n">
-        <v>1.71</v>
+        <v>5.86</v>
       </c>
       <c r="O24" t="n">
         <v>1.02</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>4.95</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45097.55208333334</v>
+        <v>45098.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>804.7</v>
+        <v>815.9</v>
       </c>
       <c r="I25" t="n">
         <v>812.1800299089348</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K25" t="n">
-        <v>1.77</v>
+        <v>0.4</v>
       </c>
       <c r="L25" t="n">
         <v>2.59</v>
@@ -1866,7 +2165,7 @@
         <v>0.77</v>
       </c>
       <c r="N25" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="O25" t="n">
         <v>-5.86</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>3.23</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45113.55208333334</v>
+        <v>45114.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>837.5</v>
+        <v>831</v>
       </c>
       <c r="I26" t="n">
         <v>836.732503772961</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K26" t="n">
-        <v>2.65</v>
+        <v>1.85</v>
       </c>
       <c r="L26" t="n">
         <v>1.27</v>
       </c>
       <c r="M26" t="n">
-        <v>0.51</v>
+        <v>0.6</v>
       </c>
       <c r="N26" t="n">
         <v>2.82</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>4.19</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45175.38541666666</v>
+        <v>45175.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>792.9</v>
+        <v>799.8</v>
       </c>
       <c r="I27" t="n">
         <v>798.8486543770366</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>61</v>
+        <v>61.16666666666666</v>
       </c>
       <c r="K27" t="n">
-        <v>4.58</v>
+        <v>3.75</v>
       </c>
       <c r="L27" t="n">
         <v>2.53</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>3.07</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45187.55208333334</v>
+        <v>45189.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>814.8</v>
+        <v>782.6</v>
       </c>
       <c r="I28" t="n">
         <v>808.9180643660894</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>12</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K28" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M28" t="n">
         <v>1.88</v>
       </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.29</v>
-      </c>
       <c r="N28" t="n">
-        <v>1.65</v>
+        <v>3.9</v>
       </c>
       <c r="O28" t="n">
         <v>1.56</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>4.86</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45251.38541666666</v>
+        <v>45251.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>757.2</v>
+        <v>758.8</v>
       </c>
       <c r="I29" t="n">
         <v>758.7179679591384</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>62</v>
+        <v>62.16666666666666</v>
       </c>
       <c r="K29" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="L29" t="n">
         <v>2.16</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>2.27</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45299.38541666666</v>
+        <v>45299.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>834.6</v>
+        <v>831.4</v>
       </c>
       <c r="I30" t="n">
         <v>831.6825987295126</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>47.83333333333334</v>
+        <v>48</v>
       </c>
       <c r="K30" t="n">
-        <v>9.99</v>
+        <v>9.57</v>
       </c>
       <c r="L30" t="n">
         <v>0.92</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>3.4</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45341.55208333334</v>
+        <v>45342.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>709.6</v>
+        <v>722</v>
       </c>
       <c r="I31" t="n">
         <v>715.4416611053651</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>42</v>
+        <v>42.83333333333334</v>
       </c>
       <c r="K31" t="n">
-        <v>14.65</v>
+        <v>13.16</v>
       </c>
       <c r="L31" t="n">
         <v>1.25</v>
@@ -2208,7 +2579,7 @@
         <v>0.91</v>
       </c>
       <c r="N31" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="O31" t="n">
         <v>-0.96</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.06</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45397.38541666666</v>
+        <v>45397.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>750.3</v>
+        <v>747</v>
       </c>
       <c r="I32" t="n">
         <v>748.4483767285006</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>55</v>
+        <v>55.16666666666666</v>
       </c>
       <c r="K32" t="n">
-        <v>3.92</v>
+        <v>3.46</v>
       </c>
       <c r="L32" t="n">
         <v>3.24</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>3.2</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45435.38541666666</v>
+        <v>45435.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>739.3</v>
+        <v>746</v>
       </c>
       <c r="I33" t="n">
         <v>742.9746957714284</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>37.83333333333334</v>
+        <v>38</v>
       </c>
       <c r="K33" t="n">
-        <v>1.03</v>
+        <v>0.13</v>
       </c>
       <c r="L33" t="n">
         <v>4.24</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>3.54</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>786.5</v>
+        <v>743.3</v>
       </c>
       <c r="I34" t="n">
         <v>754.9393828069493</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>5.43</v>
+        <v>-0.36</v>
       </c>
       <c r="L34" t="n">
-        <v>1.05</v>
+        <v>2.55</v>
       </c>
       <c r="M34" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="N34" t="n">
-        <v>1.39</v>
+        <v>4.45</v>
       </c>
       <c r="O34" t="n">
         <v>1.93</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>7.85</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45457.55208333334</v>
+        <v>45461.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>797.8</v>
+        <v>802.8</v>
       </c>
       <c r="I35" t="n">
         <v>798.288189933734</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.33</v>
+        <v>-8</v>
       </c>
       <c r="L35" t="n">
-        <v>7.56</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M35" t="n">
         <v>1.23</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>4.06</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45477.55208333334</v>
+        <v>45478.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>864</v>
+        <v>824.7</v>
       </c>
       <c r="I36" t="n">
         <v>853.1390391379105</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K36" t="n">
-        <v>7.62</v>
+        <v>2.73</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>0.88</v>
+        <v>2.49</v>
       </c>
       <c r="N36" t="n">
-        <v>2.28</v>
+        <v>4.51</v>
       </c>
       <c r="O36" t="n">
         <v>0.78</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>6.33</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45505.55208333334</v>
+        <v>45506.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>823.8</v>
+        <v>831.2</v>
       </c>
       <c r="I37" t="n">
         <v>828.122863582566</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K37" t="n">
-        <v>0.11</v>
+        <v>-0.79</v>
       </c>
       <c r="L37" t="n">
         <v>2.16</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>4.63</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45565.55208333334</v>
+        <v>45566.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>866</v>
+        <v>861.6</v>
       </c>
       <c r="I38" t="n">
         <v>864.3267210008336</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K38" t="n">
-        <v>4.19</v>
+        <v>3.66</v>
       </c>
       <c r="L38" t="n">
         <v>4.16</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>3.51</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45580.55208333334</v>
+        <v>45581.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="I39" t="n">
         <v>848.6175172277138</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K39" t="n">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="L39" t="n">
         <v>1.09</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>4.12</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>859.5</v>
+        <v>851.2</v>
       </c>
       <c r="I40" t="n">
         <v>855.1265374183104</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K40" t="n">
-        <v>0.88</v>
+        <v>-0.09</v>
       </c>
       <c r="L40" t="n">
         <v>2.93</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>4.81</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>871</v>
+        <v>887.3</v>
       </c>
       <c r="I41" t="n">
         <v>882.0062187998467</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.33</v>
+        <v>-4.24</v>
       </c>
       <c r="L41" t="n">
-        <v>3.32</v>
+        <v>4.91</v>
       </c>
       <c r="M41" t="n">
-        <v>0.77</v>
+        <v>2.47</v>
       </c>
       <c r="N41" t="n">
-        <v>1.62</v>
+        <v>2.18</v>
       </c>
       <c r="O41" t="n">
         <v>-1.79</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>4.11</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45644.55208333334</v>
+        <v>45645.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>906</v>
+        <v>897.4</v>
       </c>
       <c r="I42" t="n">
         <v>904.5043323446118</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>2.11</v>
+        <v>1.14</v>
       </c>
       <c r="L42" t="n">
         <v>0.55</v>
       </c>
       <c r="M42" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="N42" t="n">
         <v>1.71</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>3.18</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45687.38541666666</v>
+        <v>45687.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="I43" t="n">
         <v>844.1633071836006</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K43" t="n">
-        <v>5.95</v>
+        <v>5.62</v>
       </c>
       <c r="L43" t="n">
         <v>1.13</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>3.53</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45709.55208333334</v>
+        <v>45712.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>845</v>
+        <v>837</v>
       </c>
       <c r="I44" t="n">
         <v>842.039479227685</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>22</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.24</v>
+        <v>-1.18</v>
       </c>
       <c r="L44" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="M44" t="n">
         <v>1.3</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>3.29</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45716.38541666666</v>
+        <v>45716.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>856.6</v>
+        <v>865.1</v>
       </c>
       <c r="I45" t="n">
         <v>864.5076449555795</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.34</v>
+        <v>-3.36</v>
       </c>
       <c r="L45" t="n">
-        <v>3.01</v>
+        <v>3.78</v>
       </c>
       <c r="M45" t="n">
         <v>0.11</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>3.83</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>908</v>
+        <v>872.1</v>
       </c>
       <c r="I46" t="n">
         <v>883.8363767448334</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>35</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K46" t="n">
-        <v>4.96</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L46" t="n">
         <v>3.48</v>
       </c>
       <c r="M46" t="n">
-        <v>1.29</v>
+        <v>2.93</v>
       </c>
       <c r="N46" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="O46" t="n">
         <v>1.88</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>5.92</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>902.6</v>
+        <v>934.4</v>
       </c>
       <c r="I47" t="n">
         <v>919.1518760819363</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.5</v>
+        <v>-7.14</v>
       </c>
       <c r="L47" t="n">
-        <v>4.31</v>
+        <v>7.6</v>
       </c>
       <c r="M47" t="n">
-        <v>0.48</v>
+        <v>3.31</v>
       </c>
       <c r="N47" t="n">
-        <v>2.2</v>
+        <v>3.35</v>
       </c>
       <c r="O47" t="n">
         <v>-3.08</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,25 +3731,25 @@
         <v>5.25</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>970</v>
+        <v>960.4</v>
       </c>
       <c r="I48" t="n">
         <v>962.9247699353548</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K48" t="n">
-        <v>3.81</v>
+        <v>2.78</v>
       </c>
       <c r="L48" t="n">
         <v>0.74</v>
       </c>
       <c r="M48" t="n">
-        <v>0.6</v>
+        <v>1.03</v>
       </c>
       <c r="N48" t="n">
         <v>1.8</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>2.9</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45832.55208333334</v>
+        <v>45833.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>981</v>
+        <v>988.6</v>
       </c>
       <c r="I49" t="n">
         <v>985.0008607241823</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.14</v>
+        <v>-2.94</v>
       </c>
       <c r="L49" t="n">
-        <v>3.03</v>
+        <v>3.14</v>
       </c>
       <c r="M49" t="n">
         <v>0.87</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>2.91</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45856.38541666666</v>
+        <v>45856.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>984.2</v>
+        <v>978</v>
       </c>
       <c r="I50" t="n">
         <v>982.0742044834838</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.45</v>
+        <v>-1.07</v>
       </c>
       <c r="L50" t="n">
-        <v>0.67</v>
+        <v>1.22</v>
       </c>
       <c r="M50" t="n">
         <v>0.49</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>2.92</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45860.55208333334</v>
+        <v>45861.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1002.5</v>
+        <v>1010</v>
       </c>
       <c r="I51" t="n">
         <v>1006.563430449796</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.51</v>
+        <v>-3.27</v>
       </c>
       <c r="L51" t="n">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="M51" t="n">
         <v>1.13</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>3.05</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45876.55208333334</v>
+        <v>45877.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>999.7</v>
+        <v>988.8</v>
       </c>
       <c r="I52" t="n">
         <v>989.6471209140117</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.02</v>
+        <v>-2.1</v>
       </c>
       <c r="L52" t="n">
         <v>2.69</v>
       </c>
       <c r="M52" t="n">
-        <v>0.49</v>
+        <v>0.61</v>
       </c>
       <c r="N52" t="n">
-        <v>1.09</v>
+        <v>1.37</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>2.81</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45905.55208333334</v>
+        <v>45908.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>962.6</v>
+        <v>971.2</v>
       </c>
       <c r="I53" t="n">
         <v>967.7816950274853</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K53" t="n">
-        <v>2.65</v>
+        <v>1.78</v>
       </c>
       <c r="L53" t="n">
         <v>2.48</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,25 +4145,25 @@
         <v>3.39</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45923.55208333334</v>
+        <v>45924.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>958.45</v>
+        <v>949.4</v>
       </c>
       <c r="I54" t="n">
         <v>951.7406034387517</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.31</v>
+        <v>-2.24</v>
       </c>
       <c r="L54" t="n">
-        <v>1.62</v>
+        <v>2.9</v>
       </c>
       <c r="M54" t="n">
-        <v>0.54</v>
+        <v>0.65</v>
       </c>
       <c r="N54" t="n">
         <v>0.92</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>2.82</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45933.55208333334</v>
+        <v>45936.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>964</v>
+        <v>976.65</v>
       </c>
       <c r="I55" t="n">
         <v>971.4814562292854</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.54</v>
+        <v>-2.87</v>
       </c>
       <c r="L55" t="n">
-        <v>2.13</v>
+        <v>2.95</v>
       </c>
       <c r="M55" t="n">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="N55" t="n">
         <v>1.45</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>3.91</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46007.55208333334</v>
+        <v>46008.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>994.2</v>
+        <v>981.2</v>
       </c>
       <c r="I56" t="n">
         <v>981.7167696981051</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>71.16666666666667</v>
+        <v>72</v>
       </c>
       <c r="K56" t="n">
-        <v>1.8</v>
+        <v>0.47</v>
       </c>
       <c r="L56" t="n">
         <v>1.5</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>3.37</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>927.7</v>
+        <v>950.5</v>
       </c>
       <c r="I57" t="n">
         <v>945.1528078940805</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K57" t="n">
-        <v>5.45</v>
+        <v>3.13</v>
       </c>
       <c r="L57" t="n">
         <v>2.57</v>
       </c>
       <c r="M57" t="n">
-        <v>1.19</v>
+        <v>6.04</v>
       </c>
       <c r="N57" t="n">
-        <v>1.33</v>
+        <v>2.15</v>
       </c>
       <c r="O57" t="n">
         <v>-0.85</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>3.7</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46065.55208333334</v>
+        <v>46066.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>919.8</v>
+        <v>914.9</v>
       </c>
       <c r="I58" t="n">
         <v>915.3167665489553</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.23</v>
+        <v>-3.75</v>
       </c>
       <c r="L58" t="n">
-        <v>3.37</v>
+        <v>4.11</v>
       </c>
       <c r="M58" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>0.92</v>
+        <v>1.72</v>
       </c>
       <c r="O58" t="n">
         <v>2.15</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>3.84</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>772.4</v>
+        <v>810.7</v>
       </c>
       <c r="I59" t="n">
         <v>786.6725023063495</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K59" t="n">
-        <v>15.58</v>
+        <v>11.39</v>
       </c>
       <c r="L59" t="n">
         <v>1.6</v>
       </c>
       <c r="M59" t="n">
-        <v>1.71</v>
+        <v>3.57</v>
       </c>
       <c r="N59" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="O59" t="n">
         <v>-1.72</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.45</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46150.55208333334</v>
+        <v>46153.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>781.25</v>
+        <v>771.25</v>
       </c>
       <c r="I60" t="n">
         <v>772.3490378724491</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.63</v>
+        <v>-4.87</v>
       </c>
       <c r="L60" t="n">
         <v>5.98</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>4.38</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46167.38541666666</v>
+        <v>46167.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>784.9</v>
+        <v>787.45</v>
       </c>
       <c r="I61" t="n">
         <v>785.5366895509763</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.77</v>
+        <v>-2.1</v>
       </c>
       <c r="L61" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="M61" t="n">
         <v>0.91</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>4.39</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46169.55208333334</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>759.25</v>
+        <v>753.7</v>
       </c>
       <c r="I62" t="n">
         <v>755.0664452907982</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.58</v>
+        <v>-4.29</v>
       </c>
       <c r="L62" t="n">
-        <v>3.88</v>
+        <v>5.26</v>
       </c>
       <c r="M62" t="n">
-        <v>1.38</v>
+        <v>1.74</v>
       </c>
       <c r="N62" t="n">
         <v>2.69</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>4.39</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46185.38541666666</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>759.5</v>
+        <v>772</v>
       </c>
       <c r="I63" t="n">
         <v>766.7255505896694</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.77</v>
+        <v>-2.43</v>
       </c>
       <c r="L63" t="n">
-        <v>1.04</v>
+        <v>2.75</v>
       </c>
       <c r="M63" t="n">
         <v>1.26</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>5.19</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46220.55208333334</v>
+        <v>46223.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>820.8</v>
+        <v>780.5</v>
       </c>
       <c r="I64" t="n">
         <v>804.1942640317852</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>35</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K64" t="n">
-        <v>6.32</v>
+        <v>1.1</v>
       </c>
       <c r="L64" t="n">
         <v>1.66</v>
       </c>
       <c r="M64" t="n">
-        <v>1.53</v>
+        <v>3.75</v>
       </c>
       <c r="N64" t="n">
-        <v>2.49</v>
+        <v>5.22</v>
       </c>
       <c r="O64" t="n">
         <v>3.58</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>5.07</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46276.38541666666</v>
+        <v>46276.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>686.7</v>
+        <v>708.6</v>
       </c>
       <c r="I65" t="n">
         <v>707.0504687568293</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>53</v>
+        <v>53.16666666666666</v>
       </c>
       <c r="K65" t="n">
-        <v>12.02</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="L65" t="n">
         <v>1.22</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>5.29</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46293.55208333334</v>
+        <v>46294.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>719</v>
+        <v>711.6</v>
       </c>
       <c r="I66" t="n">
         <v>717.8277739558279</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K66" t="n">
-        <v>1.47</v>
+        <v>0.42</v>
       </c>
       <c r="L66" t="n">
         <v>3.15</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>3.78</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46309.55208333334</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>710.5</v>
+        <v>725.6</v>
       </c>
       <c r="I67" t="n">
         <v>720.9546632870871</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K67" t="n">
-        <v>0.15</v>
+        <v>-1.97</v>
       </c>
       <c r="L67" t="n">
         <v>3.18</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,25 +5111,25 @@
         <v>4.79</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>712</v>
+        <v>700.3</v>
       </c>
       <c r="I68" t="n">
         <v>703.6756330488569</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.87</v>
+        <v>-3.49</v>
       </c>
       <c r="L68" t="n">
-        <v>2.54</v>
+        <v>3.51</v>
       </c>
       <c r="M68" t="n">
-        <v>-0</v>
+        <v>0.34</v>
       </c>
       <c r="N68" t="n">
         <v>2.1</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,14 @@
       <c r="Q69" t="n">
         <v>12</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6479,7 +7314,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -6489,7 +7324,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="7">
@@ -6499,7 +7334,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="8">
@@ -6509,7 +7344,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6519,7 +7354,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36.4</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="10">
@@ -6529,7 +7364,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53.9</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="11">
@@ -6539,7 +7374,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -6549,7 +7384,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -6559,7 +7394,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67.2</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="14">
@@ -6569,7 +7404,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.74</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="15">
@@ -6579,7 +7414,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.84</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
@@ -6589,7 +7424,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.63</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="17">
@@ -6599,7 +7434,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15.58</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="18">
@@ -6609,7 +7444,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56.7</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +7454,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.46</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="20">
@@ -6629,7 +7464,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.19</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="21">
@@ -6639,7 +7474,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.56</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -6649,7 +7484,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -6669,7 +7504,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.03</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="25">
@@ -6679,7 +7514,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.33</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="26">
@@ -6689,7 +7524,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.23</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="27">
@@ -6709,7 +7544,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
